--- a/reports/group_3_subject_1_report.xlsx
+++ b/reports/group_3_subject_1_report.xlsx
@@ -4,14 +4,14 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="Оценки по биология" state="visible" r:id="rId4"/>
+    <sheet sheetId="1" name="Оценки по Гашишоведение" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="18">
   <si>
     <t>№</t>
   </si>
@@ -25,22 +25,40 @@
     <t>Дата оценки</t>
   </si>
   <si>
-    <t>Димммммаааа</t>
+    <t>New</t>
+  </si>
+  <si>
+    <t>Нет оценки</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>prohor</t>
   </si>
   <si>
     <t>хорошо</t>
   </si>
   <si>
-    <t>5/16/2025</t>
-  </si>
-  <si>
-    <t>Димас</t>
+    <t>5/17/2025</t>
+  </si>
+  <si>
+    <t>cxzczxc</t>
+  </si>
+  <si>
+    <t>tujh</t>
+  </si>
+  <si>
+    <t>незачет</t>
+  </si>
+  <si>
+    <t>DENISPIDOR</t>
   </si>
   <si>
     <t>Предмет:</t>
   </si>
   <si>
-    <t>биология</t>
+    <t>Гашишоведение</t>
   </si>
   <si>
     <t>Всего студентов:</t>
@@ -423,7 +441,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -462,24 +480,24 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
         <v>5</v>
@@ -488,28 +506,56 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>8</v>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7">
-        <v>2</v>
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8">
-        <v>3</v>
+        <v>14</v>
+      </c>
+      <c r="B8" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
